--- a/summaries/summary_report_absolute.xlsx
+++ b/summaries/summary_report_absolute.xlsx
@@ -1032,7 +1032,7 @@
         <v>10.67</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>44.24</v>
+        <v>46.41</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>6.7</v>
@@ -1053,13 +1053,13 @@
         <v>10.56</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>40.2</v>
+        <v>41.92</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>40.44</v>
+        <v>42.17</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>100</v>
       </c>
       <c r="BV5" s="6" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="BW5" s="6" t="n">
         <v>100</v>
@@ -1312,7 +1312,7 @@
       <c r="M6" s="10" t="n">
         <v>97.8</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="10" t="n">
         <v>40.76</v>
       </c>
       <c r="O6" s="9" t="n">
@@ -1793,7 +1793,7 @@
       <c r="D8" s="9" t="n">
         <v>46.01</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>44.35</v>
       </c>
       <c r="F8" s="9" t="n">
@@ -2000,7 +2000,7 @@
       <c r="BU8" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="BV8" s="9" t="n">
+      <c r="BV8" s="10" t="n">
         <v>5.77</v>
       </c>
       <c r="BW8" s="11" t="n">
@@ -2294,7 +2294,7 @@
         <v>26.66</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>51.33</v>
+        <v>55.08</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>29.28</v>
@@ -2315,13 +2315,13 @@
         <v>39.52</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>48.74</v>
+        <v>53.53</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>48.94</v>
+        <v>53.74</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>57.5</v>
@@ -2501,7 +2501,7 @@
         <v>100</v>
       </c>
       <c r="BV10" s="6" t="n">
-        <v>0</v>
+        <v>24.04</v>
       </c>
       <c r="BW10" s="6" t="n">
         <v>100</v>
@@ -2547,7 +2547,7 @@
       <c r="D11" s="9" t="n">
         <v>31.58</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>54.27</v>
       </c>
       <c r="F11" s="9" t="n">
@@ -2568,13 +2568,13 @@
       <c r="K11" s="10" t="n">
         <v>35.32</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="10" t="n">
         <v>50.32</v>
       </c>
       <c r="M11" s="11" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="N11" s="9" t="n">
+      <c r="N11" s="10" t="n">
         <v>50.52</v>
       </c>
       <c r="O11" s="9" t="n">
@@ -2754,7 +2754,7 @@
       <c r="BU11" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="BV11" s="9" t="n">
+      <c r="BV11" s="10" t="n">
         <v>20.19</v>
       </c>
       <c r="BW11" s="11" t="n">
@@ -3055,7 +3055,7 @@
       <c r="D13" s="9" t="n">
         <v>33.35</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <v>54.27</v>
       </c>
       <c r="F13" s="9" t="n">
@@ -3076,13 +3076,13 @@
       <c r="K13" s="10" t="n">
         <v>35.32</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="10" t="n">
         <v>50.32</v>
       </c>
       <c r="M13" s="11" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="N13" s="9" t="n">
+      <c r="N13" s="10" t="n">
         <v>50.52</v>
       </c>
       <c r="O13" s="9" t="n">
@@ -3262,7 +3262,7 @@
       <c r="BU13" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="BV13" s="9" t="n">
+      <c r="BV13" s="10" t="n">
         <v>20.19</v>
       </c>
       <c r="BW13" s="11" t="n">
@@ -3548,7 +3548,7 @@
         <v>31.91</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>53.9</v>
+        <v>57.49</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>37.37</v>
@@ -3569,13 +3569,13 @@
         <v>45.07</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>50.2</v>
+        <v>53.85</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>100</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>50.2</v>
+        <v>53.85</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>87.5</v>
@@ -3755,7 +3755,7 @@
         <v>100</v>
       </c>
       <c r="BV15" s="6" t="n">
-        <v>0</v>
+        <v>18.27</v>
       </c>
       <c r="BW15" s="6" t="n">
         <v>100</v>
@@ -4008,7 +4008,7 @@
       <c r="BU16" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="BV16" s="9" t="n">
+      <c r="BV16" s="10" t="n">
         <v>1.92</v>
       </c>
       <c r="BW16" s="11" t="n">
@@ -4056,7 +4056,7 @@
         <v>34.39</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>53.26</v>
+        <v>56.85</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>40.09</v>
@@ -4076,14 +4076,14 @@
       <c r="K17" s="10" t="n">
         <v>44.2</v>
       </c>
-      <c r="L17" s="10" t="n">
-        <v>50.1</v>
+      <c r="L17" s="9" t="n">
+        <v>54.33</v>
       </c>
       <c r="M17" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N17" s="10" t="n">
-        <v>50.1</v>
+      <c r="N17" s="9" t="n">
+        <v>54.33</v>
       </c>
       <c r="O17" s="10" t="n">
         <v>77.5</v>
@@ -4262,8 +4262,8 @@
       <c r="BU17" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="BV17" s="11" t="n">
-        <v>0</v>
+      <c r="BV17" s="9" t="n">
+        <v>21.15</v>
       </c>
       <c r="BW17" s="11" t="n">
         <v>100</v>
